--- a/ProductBacklog_nhom04quanlychothuexetulai.xlsx
+++ b/ProductBacklog_nhom04quanlychothuexetulai.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30326"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30527"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Admin\Desktop\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\dowload c\NAM3\CongNghePhanMemNangCao\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{F8FE2AC0-AEE2-469B-B03E-81B148748DEF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DC51BA6C-B3BE-4054-9BB3-59158C739951}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" tabRatio="500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="230" uniqueCount="137">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="258" uniqueCount="138">
   <si>
     <t>DỰ ÁN HỆ THỐNG CHO THUÊ XE - PRODUCT BACKLOG</t>
   </si>
@@ -455,6 +455,9 @@
   </si>
   <si>
     <t xml:space="preserve">Developer 1 </t>
+  </si>
+  <si>
+    <t>Phạm Trọng Phúc</t>
   </si>
 </sst>
 </file>
@@ -580,19 +583,6 @@
   </cellStyleXfs>
   <cellXfs count="21">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="3" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -610,6 +600,24 @@
     </xf>
     <xf numFmtId="0" fontId="0" fillId="4" borderId="1" xfId="0" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="7" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
+    <xf numFmtId="15" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="6" borderId="1" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="6" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="0" fontId="3" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
@@ -619,11 +627,6 @@
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
-    <xf numFmtId="15" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="6" borderId="1" xfId="0" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="6" borderId="0" xfId="0" applyFill="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -897,417 +900,417 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:3" ht="21.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A1" s="5" t="s">
+      <c r="A1" s="15" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="5"/>
-      <c r="C1" s="5"/>
+      <c r="B1" s="15"/>
+      <c r="C1" s="15"/>
     </row>
     <row r="3" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A3" s="6" t="s">
+      <c r="A3" s="1" t="s">
         <v>1</v>
       </c>
-      <c r="B3" s="6" t="s">
+      <c r="B3" s="1" t="s">
         <v>2</v>
       </c>
-      <c r="C3" s="6" t="s">
+      <c r="C3" s="1" t="s">
         <v>3</v>
       </c>
     </row>
     <row r="4" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A4" s="4" t="s">
+      <c r="A4" s="17" t="s">
         <v>4</v>
       </c>
-      <c r="B4" s="4"/>
-      <c r="C4" s="4"/>
+      <c r="B4" s="17"/>
+      <c r="C4" s="17"/>
     </row>
     <row r="5" spans="1:3" ht="39.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A5" s="7" t="s">
+      <c r="A5" s="2" t="s">
         <v>5</v>
       </c>
-      <c r="B5" s="8" t="s">
+      <c r="B5" s="3" t="s">
         <v>6</v>
       </c>
-      <c r="C5" s="7">
+      <c r="C5" s="2">
         <v>8</v>
       </c>
     </row>
     <row r="6" spans="1:3" ht="39.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A6" s="7" t="s">
+      <c r="A6" s="2" t="s">
         <v>7</v>
       </c>
-      <c r="B6" s="8" t="s">
-        <v>8</v>
-      </c>
-      <c r="C6" s="7">
+      <c r="B6" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="C6" s="2">
         <v>5</v>
       </c>
     </row>
     <row r="7" spans="1:3" ht="39.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A7" s="7" t="s">
+      <c r="A7" s="2" t="s">
         <v>9</v>
       </c>
-      <c r="B7" s="8" t="s">
+      <c r="B7" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="C7" s="7">
+      <c r="C7" s="2">
         <v>5</v>
       </c>
     </row>
     <row r="8" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A8" s="4" t="s">
+      <c r="A8" s="17" t="s">
         <v>11</v>
       </c>
-      <c r="B8" s="4"/>
-      <c r="C8" s="4"/>
+      <c r="B8" s="17"/>
+      <c r="C8" s="17"/>
     </row>
     <row r="9" spans="1:3" ht="39.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A9" s="7" t="s">
+      <c r="A9" s="2" t="s">
         <v>12</v>
       </c>
-      <c r="B9" s="8" t="s">
+      <c r="B9" s="3" t="s">
         <v>13</v>
       </c>
-      <c r="C9" s="7">
+      <c r="C9" s="2">
         <v>8</v>
       </c>
     </row>
     <row r="10" spans="1:3" ht="39.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A10" s="7" t="s">
+      <c r="A10" s="2" t="s">
         <v>14</v>
       </c>
-      <c r="B10" s="8" t="s">
+      <c r="B10" s="3" t="s">
         <v>15</v>
       </c>
-      <c r="C10" s="7">
+      <c r="C10" s="2">
         <v>8</v>
       </c>
     </row>
     <row r="11" spans="1:3" ht="39.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A11" s="7" t="s">
+      <c r="A11" s="2" t="s">
         <v>16</v>
       </c>
-      <c r="B11" s="8" t="s">
+      <c r="B11" s="3" t="s">
         <v>17</v>
       </c>
-      <c r="C11" s="7">
+      <c r="C11" s="2">
         <v>5</v>
       </c>
     </row>
     <row r="12" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A12" s="4" t="s">
+      <c r="A12" s="17" t="s">
         <v>18</v>
       </c>
-      <c r="B12" s="4"/>
-      <c r="C12" s="4"/>
+      <c r="B12" s="17"/>
+      <c r="C12" s="17"/>
     </row>
     <row r="13" spans="1:3" ht="39.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A13" s="7" t="s">
+      <c r="A13" s="2" t="s">
         <v>19</v>
       </c>
-      <c r="B13" s="8" t="s">
+      <c r="B13" s="3" t="s">
         <v>20</v>
       </c>
-      <c r="C13" s="7">
+      <c r="C13" s="2">
         <v>5</v>
       </c>
     </row>
     <row r="14" spans="1:3" ht="39.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A14" s="7" t="s">
+      <c r="A14" s="2" t="s">
         <v>21</v>
       </c>
-      <c r="B14" s="8" t="s">
+      <c r="B14" s="3" t="s">
         <v>22</v>
       </c>
-      <c r="C14" s="7">
+      <c r="C14" s="2">
         <v>8</v>
       </c>
     </row>
     <row r="15" spans="1:3" ht="39.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A15" s="7" t="s">
+      <c r="A15" s="2" t="s">
         <v>23</v>
       </c>
-      <c r="B15" s="8" t="s">
+      <c r="B15" s="3" t="s">
         <v>24</v>
       </c>
-      <c r="C15" s="7">
+      <c r="C15" s="2">
         <v>5</v>
       </c>
     </row>
     <row r="16" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A16" s="4" t="s">
+      <c r="A16" s="17" t="s">
         <v>25</v>
       </c>
-      <c r="B16" s="4"/>
-      <c r="C16" s="4"/>
+      <c r="B16" s="17"/>
+      <c r="C16" s="17"/>
     </row>
     <row r="17" spans="1:3" ht="39.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A17" s="7" t="s">
+      <c r="A17" s="2" t="s">
         <v>26</v>
       </c>
-      <c r="B17" s="8" t="s">
+      <c r="B17" s="3" t="s">
         <v>27</v>
       </c>
-      <c r="C17" s="7">
+      <c r="C17" s="2">
         <v>5</v>
       </c>
     </row>
     <row r="18" spans="1:3" ht="39.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A18" s="7" t="s">
+      <c r="A18" s="2" t="s">
         <v>28</v>
       </c>
-      <c r="B18" s="8" t="s">
+      <c r="B18" s="3" t="s">
         <v>29</v>
       </c>
-      <c r="C18" s="7">
+      <c r="C18" s="2">
         <v>8</v>
       </c>
     </row>
     <row r="19" spans="1:3" ht="39.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A19" s="7" t="s">
+      <c r="A19" s="2" t="s">
         <v>30</v>
       </c>
-      <c r="B19" s="8" t="s">
+      <c r="B19" s="3" t="s">
         <v>31</v>
       </c>
-      <c r="C19" s="7">
+      <c r="C19" s="2">
         <v>8</v>
       </c>
     </row>
     <row r="20" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A20" s="4" t="s">
+      <c r="A20" s="17" t="s">
         <v>32</v>
       </c>
-      <c r="B20" s="4"/>
-      <c r="C20" s="4"/>
+      <c r="B20" s="17"/>
+      <c r="C20" s="17"/>
     </row>
     <row r="21" spans="1:3" ht="39.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A21" s="7" t="s">
+      <c r="A21" s="2" t="s">
         <v>33</v>
       </c>
-      <c r="B21" s="8" t="s">
+      <c r="B21" s="3" t="s">
         <v>34</v>
       </c>
-      <c r="C21" s="7">
+      <c r="C21" s="2">
         <v>8</v>
       </c>
     </row>
     <row r="22" spans="1:3" ht="39.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A22" s="7" t="s">
+      <c r="A22" s="2" t="s">
         <v>35</v>
       </c>
-      <c r="B22" s="8" t="s">
+      <c r="B22" s="3" t="s">
         <v>36</v>
       </c>
-      <c r="C22" s="7">
+      <c r="C22" s="2">
         <v>5</v>
       </c>
     </row>
     <row r="23" spans="1:3" ht="39.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A23" s="7" t="s">
+      <c r="A23" s="2" t="s">
         <v>37</v>
       </c>
-      <c r="B23" s="8" t="s">
+      <c r="B23" s="3" t="s">
         <v>38</v>
       </c>
-      <c r="C23" s="7">
+      <c r="C23" s="2">
         <v>3</v>
       </c>
     </row>
     <row r="24" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A24" s="4" t="s">
+      <c r="A24" s="17" t="s">
         <v>39</v>
       </c>
-      <c r="B24" s="4"/>
-      <c r="C24" s="4"/>
+      <c r="B24" s="17"/>
+      <c r="C24" s="17"/>
     </row>
     <row r="25" spans="1:3" ht="39.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A25" s="7" t="s">
+      <c r="A25" s="2" t="s">
         <v>40</v>
       </c>
-      <c r="B25" s="8" t="s">
+      <c r="B25" s="3" t="s">
         <v>41</v>
       </c>
-      <c r="C25" s="7">
+      <c r="C25" s="2">
         <v>8</v>
       </c>
     </row>
     <row r="26" spans="1:3" ht="39.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A26" s="7" t="s">
+      <c r="A26" s="2" t="s">
         <v>42</v>
       </c>
-      <c r="B26" s="8" t="s">
+      <c r="B26" s="3" t="s">
         <v>43</v>
       </c>
-      <c r="C26" s="7">
+      <c r="C26" s="2">
         <v>5</v>
       </c>
     </row>
     <row r="27" spans="1:3" ht="39.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A27" s="7" t="s">
+      <c r="A27" s="2" t="s">
         <v>44</v>
       </c>
-      <c r="B27" s="8" t="s">
+      <c r="B27" s="3" t="s">
         <v>45</v>
       </c>
-      <c r="C27" s="7">
+      <c r="C27" s="2">
         <v>8</v>
       </c>
     </row>
     <row r="28" spans="1:3" ht="39.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A28" s="7" t="s">
+      <c r="A28" s="2" t="s">
         <v>46</v>
       </c>
-      <c r="B28" s="8" t="s">
+      <c r="B28" s="3" t="s">
         <v>47</v>
       </c>
-      <c r="C28" s="7">
+      <c r="C28" s="2">
         <v>8</v>
       </c>
     </row>
     <row r="29" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A29" s="4" t="s">
+      <c r="A29" s="17" t="s">
         <v>48</v>
       </c>
-      <c r="B29" s="4"/>
-      <c r="C29" s="4"/>
+      <c r="B29" s="17"/>
+      <c r="C29" s="17"/>
     </row>
     <row r="30" spans="1:3" ht="39.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A30" s="7" t="s">
+      <c r="A30" s="2" t="s">
         <v>49</v>
       </c>
-      <c r="B30" s="8" t="s">
+      <c r="B30" s="3" t="s">
         <v>50</v>
       </c>
-      <c r="C30" s="7">
+      <c r="C30" s="2">
         <v>8</v>
       </c>
     </row>
     <row r="31" spans="1:3" ht="39.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A31" s="7" t="s">
+      <c r="A31" s="2" t="s">
         <v>51</v>
       </c>
-      <c r="B31" s="8" t="s">
+      <c r="B31" s="3" t="s">
         <v>52</v>
       </c>
-      <c r="C31" s="7">
+      <c r="C31" s="2">
         <v>5</v>
       </c>
     </row>
     <row r="32" spans="1:3" ht="39.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A32" s="7" t="s">
+      <c r="A32" s="2" t="s">
         <v>53</v>
       </c>
-      <c r="B32" s="8" t="s">
+      <c r="B32" s="3" t="s">
         <v>54</v>
       </c>
-      <c r="C32" s="7">
+      <c r="C32" s="2">
         <v>5</v>
       </c>
     </row>
     <row r="33" spans="1:3" ht="39.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A33" s="7" t="s">
+      <c r="A33" s="2" t="s">
         <v>55</v>
       </c>
-      <c r="B33" s="8" t="s">
+      <c r="B33" s="3" t="s">
         <v>56</v>
       </c>
-      <c r="C33" s="7">
+      <c r="C33" s="2">
         <v>13</v>
       </c>
     </row>
     <row r="34" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A34" s="4" t="s">
+      <c r="A34" s="17" t="s">
         <v>57</v>
       </c>
-      <c r="B34" s="4"/>
-      <c r="C34" s="4"/>
+      <c r="B34" s="17"/>
+      <c r="C34" s="17"/>
     </row>
     <row r="35" spans="1:3" ht="39.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A35" s="7" t="s">
+      <c r="A35" s="2" t="s">
         <v>58</v>
       </c>
-      <c r="B35" s="8" t="s">
+      <c r="B35" s="3" t="s">
         <v>59</v>
       </c>
-      <c r="C35" s="7">
+      <c r="C35" s="2">
         <v>8</v>
       </c>
     </row>
     <row r="36" spans="1:3" ht="39.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A36" s="7" t="s">
+      <c r="A36" s="2" t="s">
         <v>60</v>
       </c>
-      <c r="B36" s="8" t="s">
+      <c r="B36" s="3" t="s">
         <v>61</v>
       </c>
-      <c r="C36" s="7">
+      <c r="C36" s="2">
         <v>3</v>
       </c>
     </row>
     <row r="37" spans="1:3" ht="39.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A37" s="7" t="s">
+      <c r="A37" s="2" t="s">
         <v>62</v>
       </c>
-      <c r="B37" s="8" t="s">
+      <c r="B37" s="3" t="s">
         <v>63</v>
       </c>
-      <c r="C37" s="7">
+      <c r="C37" s="2">
         <v>5</v>
       </c>
     </row>
     <row r="38" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A38" s="4" t="s">
+      <c r="A38" s="17" t="s">
         <v>64</v>
       </c>
-      <c r="B38" s="4"/>
-      <c r="C38" s="4"/>
+      <c r="B38" s="17"/>
+      <c r="C38" s="17"/>
     </row>
     <row r="39" spans="1:3" ht="39.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A39" s="7" t="s">
+      <c r="A39" s="2" t="s">
         <v>65</v>
       </c>
-      <c r="B39" s="8" t="s">
+      <c r="B39" s="3" t="s">
         <v>66</v>
       </c>
-      <c r="C39" s="7">
+      <c r="C39" s="2">
         <v>8</v>
       </c>
     </row>
     <row r="40" spans="1:3" ht="39.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A40" s="7" t="s">
+      <c r="A40" s="2" t="s">
         <v>67</v>
       </c>
-      <c r="B40" s="8" t="s">
+      <c r="B40" s="3" t="s">
         <v>68</v>
       </c>
-      <c r="C40" s="7">
+      <c r="C40" s="2">
         <v>8</v>
       </c>
     </row>
     <row r="41" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A41" s="3" t="s">
+      <c r="A41" s="14" t="s">
         <v>69</v>
       </c>
-      <c r="B41" s="3"/>
-      <c r="C41" s="9">
+      <c r="B41" s="14"/>
+      <c r="C41" s="4">
         <f>SUM(C4:C40)</f>
         <v>186</v>
       </c>
     </row>
   </sheetData>
   <mergeCells count="11">
+    <mergeCell ref="A1:C1"/>
+    <mergeCell ref="A4:C4"/>
+    <mergeCell ref="A8:C8"/>
+    <mergeCell ref="A12:C12"/>
+    <mergeCell ref="A16:C16"/>
     <mergeCell ref="A41:B41"/>
     <mergeCell ref="A20:C20"/>
     <mergeCell ref="A24:C24"/>
     <mergeCell ref="A29:C29"/>
     <mergeCell ref="A34:C34"/>
     <mergeCell ref="A38:C38"/>
-    <mergeCell ref="A1:C1"/>
-    <mergeCell ref="A4:C4"/>
-    <mergeCell ref="A8:C8"/>
-    <mergeCell ref="A12:C12"/>
-    <mergeCell ref="A16:C16"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.511811023622047" footer="0.511811023622047"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300"/>
@@ -1322,887 +1325,948 @@
     <col min="1" max="1" width="10" customWidth="1"/>
     <col min="2" max="2" width="55" customWidth="1"/>
     <col min="3" max="3" width="8" customWidth="1"/>
-    <col min="4" max="4" width="16" customWidth="1"/>
+    <col min="4" max="4" width="25.21875" customWidth="1"/>
     <col min="5" max="8" width="12" customWidth="1"/>
     <col min="9" max="9" width="10" customWidth="1"/>
     <col min="10" max="10" width="22" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:10" ht="21.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A1" s="5" t="s">
+      <c r="A1" s="15" t="s">
         <v>70</v>
       </c>
-      <c r="B1" s="5"/>
-      <c r="C1" s="5"/>
-      <c r="D1" s="5"/>
-      <c r="E1" s="5"/>
-      <c r="F1" s="5"/>
-      <c r="G1" s="5"/>
-      <c r="H1" s="5"/>
-      <c r="I1" s="5"/>
-      <c r="J1" s="5"/>
+      <c r="B1" s="15"/>
+      <c r="C1" s="15"/>
+      <c r="D1" s="15"/>
+      <c r="E1" s="15"/>
+      <c r="F1" s="15"/>
+      <c r="G1" s="15"/>
+      <c r="H1" s="15"/>
+      <c r="I1" s="15"/>
+      <c r="J1" s="15"/>
     </row>
     <row r="2" spans="1:10" ht="27.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A2" s="2" t="s">
+      <c r="A2" s="16" t="s">
         <v>71</v>
       </c>
-      <c r="B2" s="2"/>
-      <c r="C2" s="2"/>
-      <c r="D2" s="2"/>
-      <c r="E2" s="2"/>
-      <c r="F2" s="2"/>
-      <c r="G2" s="2"/>
-      <c r="H2" s="2"/>
-      <c r="I2" s="2"/>
-      <c r="J2" s="2"/>
+      <c r="B2" s="16"/>
+      <c r="C2" s="16"/>
+      <c r="D2" s="16"/>
+      <c r="E2" s="16"/>
+      <c r="F2" s="16"/>
+      <c r="G2" s="16"/>
+      <c r="H2" s="16"/>
+      <c r="I2" s="16"/>
+      <c r="J2" s="16"/>
     </row>
     <row r="4" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A4" s="6" t="s">
+      <c r="A4" s="1" t="s">
         <v>1</v>
       </c>
-      <c r="B4" s="6" t="s">
+      <c r="B4" s="1" t="s">
         <v>2</v>
       </c>
-      <c r="C4" s="6" t="s">
+      <c r="C4" s="1" t="s">
         <v>3</v>
       </c>
-      <c r="D4" s="6" t="s">
+      <c r="D4" s="1" t="s">
         <v>72</v>
       </c>
-      <c r="E4" s="6" t="s">
+      <c r="E4" s="1" t="s">
         <v>73</v>
       </c>
-      <c r="F4" s="6" t="s">
+      <c r="F4" s="1" t="s">
         <v>74</v>
       </c>
-      <c r="G4" s="6" t="s">
+      <c r="G4" s="1" t="s">
         <v>75</v>
       </c>
-      <c r="H4" s="6" t="s">
+      <c r="H4" s="1" t="s">
         <v>76</v>
       </c>
-      <c r="I4" s="6" t="s">
+      <c r="I4" s="1" t="s">
         <v>77</v>
       </c>
-      <c r="J4" s="6" t="s">
+      <c r="J4" s="1" t="s">
         <v>78</v>
       </c>
     </row>
     <row r="5" spans="1:10" ht="18" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A5" s="1" t="s">
+      <c r="A5" s="13" t="s">
         <v>79</v>
       </c>
-      <c r="B5" s="1"/>
-      <c r="C5" s="10">
+      <c r="B5" s="13"/>
+      <c r="C5" s="5">
         <f>SUM(C6:C8)</f>
         <v>18</v>
       </c>
-      <c r="D5" s="11"/>
-      <c r="E5" s="11"/>
-      <c r="F5" s="11"/>
-      <c r="G5" s="11"/>
-      <c r="H5" s="11"/>
-      <c r="I5" s="11"/>
-      <c r="J5" s="11"/>
+      <c r="D5" s="6"/>
+      <c r="E5" s="6"/>
+      <c r="F5" s="6"/>
+      <c r="G5" s="6"/>
+      <c r="H5" s="6"/>
+      <c r="I5" s="6"/>
+      <c r="J5" s="6"/>
     </row>
     <row r="6" spans="1:10" ht="33.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A6" s="7" t="s">
+      <c r="A6" s="2" t="s">
         <v>5</v>
       </c>
-      <c r="B6" s="8" t="s">
+      <c r="B6" s="3" t="s">
         <v>6</v>
       </c>
-      <c r="C6" s="7">
-        <v>8</v>
-      </c>
-      <c r="D6" s="7"/>
-      <c r="E6" s="7" t="s">
+      <c r="C6" s="2">
+        <v>8</v>
+      </c>
+      <c r="D6" t="s">
+        <v>134</v>
+      </c>
+      <c r="E6" s="2" t="s">
         <v>80</v>
       </c>
-      <c r="F6" s="7" t="s">
+      <c r="F6" s="2" t="s">
         <v>81</v>
       </c>
-      <c r="G6" s="7"/>
-      <c r="H6" s="7"/>
-      <c r="I6" s="7"/>
-      <c r="J6" s="7"/>
+      <c r="G6" s="2"/>
+      <c r="H6" s="2"/>
+      <c r="I6" s="2"/>
+      <c r="J6" s="2"/>
     </row>
     <row r="7" spans="1:10" ht="33.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A7" s="7" t="s">
+      <c r="A7" s="2" t="s">
         <v>7</v>
       </c>
-      <c r="B7" s="8" t="s">
-        <v>8</v>
-      </c>
-      <c r="C7" s="7">
+      <c r="B7" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="C7" s="2">
         <v>5</v>
       </c>
-      <c r="D7" s="7"/>
-      <c r="E7" s="7" t="s">
+      <c r="D7" t="s">
+        <v>134</v>
+      </c>
+      <c r="E7" s="2" t="s">
         <v>80</v>
       </c>
-      <c r="F7" s="7" t="s">
+      <c r="F7" s="2" t="s">
         <v>81</v>
       </c>
-      <c r="G7" s="7"/>
-      <c r="H7" s="7"/>
-      <c r="I7" s="7"/>
-      <c r="J7" s="7"/>
+      <c r="G7" s="2"/>
+      <c r="H7" s="2"/>
+      <c r="I7" s="2"/>
+      <c r="J7" s="2"/>
     </row>
     <row r="8" spans="1:10" ht="33.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A8" s="7" t="s">
+      <c r="A8" s="2" t="s">
         <v>9</v>
       </c>
-      <c r="B8" s="8" t="s">
+      <c r="B8" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="C8" s="7">
+      <c r="C8" s="2">
         <v>5</v>
       </c>
-      <c r="D8" s="7"/>
-      <c r="E8" s="7" t="s">
+      <c r="D8" t="s">
+        <v>134</v>
+      </c>
+      <c r="E8" s="2" t="s">
         <v>80</v>
       </c>
-      <c r="F8" s="7" t="s">
+      <c r="F8" s="2" t="s">
         <v>81</v>
       </c>
-      <c r="G8" s="7"/>
-      <c r="H8" s="7"/>
-      <c r="I8" s="7"/>
-      <c r="J8" s="7"/>
+      <c r="G8" s="2"/>
+      <c r="H8" s="2"/>
+      <c r="I8" s="2"/>
+      <c r="J8" s="2"/>
     </row>
     <row r="9" spans="1:10" ht="18" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A9" s="1" t="s">
+      <c r="A9" s="13" t="s">
         <v>82</v>
       </c>
-      <c r="B9" s="1"/>
-      <c r="C9" s="10">
+      <c r="B9" s="13"/>
+      <c r="C9" s="5">
         <f>SUM(C10:C12)</f>
         <v>21</v>
       </c>
-      <c r="D9" s="11"/>
-      <c r="E9" s="11"/>
-      <c r="F9" s="11"/>
-      <c r="G9" s="11"/>
-      <c r="H9" s="11"/>
-      <c r="I9" s="11"/>
-      <c r="J9" s="11"/>
+      <c r="D9" s="6"/>
+      <c r="E9" s="6"/>
+      <c r="F9" s="6"/>
+      <c r="G9" s="6"/>
+      <c r="H9" s="6"/>
+      <c r="I9" s="6"/>
+      <c r="J9" s="6"/>
     </row>
     <row r="10" spans="1:10" ht="33.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A10" s="7" t="s">
+      <c r="A10" s="2" t="s">
         <v>12</v>
       </c>
-      <c r="B10" s="8" t="s">
+      <c r="B10" s="3" t="s">
         <v>13</v>
       </c>
-      <c r="C10" s="7">
-        <v>8</v>
-      </c>
-      <c r="D10" s="7"/>
-      <c r="E10" s="7" t="s">
+      <c r="C10" s="2">
+        <v>8</v>
+      </c>
+      <c r="D10" s="9" t="s">
+        <v>122</v>
+      </c>
+      <c r="E10" s="2" t="s">
         <v>83</v>
       </c>
-      <c r="F10" s="7" t="s">
+      <c r="F10" s="2" t="s">
         <v>84</v>
       </c>
-      <c r="G10" s="7"/>
-      <c r="H10" s="7"/>
-      <c r="I10" s="7"/>
-      <c r="J10" s="7"/>
+      <c r="G10" s="2"/>
+      <c r="H10" s="2"/>
+      <c r="I10" s="2"/>
+      <c r="J10" s="2"/>
     </row>
     <row r="11" spans="1:10" ht="33.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A11" s="7" t="s">
+      <c r="A11" s="2" t="s">
         <v>14</v>
       </c>
-      <c r="B11" s="8" t="s">
+      <c r="B11" s="3" t="s">
         <v>15</v>
       </c>
-      <c r="C11" s="7">
-        <v>8</v>
-      </c>
-      <c r="D11" s="7"/>
-      <c r="E11" s="7" t="s">
+      <c r="C11" s="2">
+        <v>8</v>
+      </c>
+      <c r="D11" s="9" t="s">
+        <v>122</v>
+      </c>
+      <c r="E11" s="2" t="s">
         <v>83</v>
       </c>
-      <c r="F11" s="7" t="s">
+      <c r="F11" s="2" t="s">
         <v>84</v>
       </c>
-      <c r="G11" s="7"/>
-      <c r="H11" s="7"/>
-      <c r="I11" s="7"/>
-      <c r="J11" s="7"/>
+      <c r="G11" s="2"/>
+      <c r="H11" s="2"/>
+      <c r="I11" s="2"/>
+      <c r="J11" s="2"/>
     </row>
     <row r="12" spans="1:10" ht="33.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A12" s="7" t="s">
+      <c r="A12" s="2" t="s">
         <v>16</v>
       </c>
-      <c r="B12" s="8" t="s">
+      <c r="B12" s="3" t="s">
         <v>17</v>
       </c>
-      <c r="C12" s="7">
+      <c r="C12" s="2">
         <v>5</v>
       </c>
-      <c r="D12" s="7"/>
-      <c r="E12" s="7" t="s">
+      <c r="D12" s="9" t="s">
+        <v>122</v>
+      </c>
+      <c r="E12" s="2" t="s">
         <v>83</v>
       </c>
-      <c r="F12" s="7" t="s">
+      <c r="F12" s="2" t="s">
         <v>84</v>
       </c>
-      <c r="G12" s="7"/>
-      <c r="H12" s="7"/>
-      <c r="I12" s="7"/>
-      <c r="J12" s="7"/>
+      <c r="G12" s="2"/>
+      <c r="H12" s="2"/>
+      <c r="I12" s="2"/>
+      <c r="J12" s="2"/>
     </row>
     <row r="13" spans="1:10" ht="18" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A13" s="1" t="s">
+      <c r="A13" s="13" t="s">
         <v>85</v>
       </c>
-      <c r="B13" s="1"/>
-      <c r="C13" s="10">
+      <c r="B13" s="13"/>
+      <c r="C13" s="5">
         <f>SUM(C14:C16)</f>
         <v>18</v>
       </c>
-      <c r="D13" s="11"/>
-      <c r="E13" s="11"/>
-      <c r="F13" s="11"/>
-      <c r="G13" s="11"/>
-      <c r="H13" s="11"/>
-      <c r="I13" s="11"/>
-      <c r="J13" s="11"/>
+      <c r="D13" s="6"/>
+      <c r="E13" s="6"/>
+      <c r="F13" s="6"/>
+      <c r="G13" s="6"/>
+      <c r="H13" s="6"/>
+      <c r="I13" s="6"/>
+      <c r="J13" s="6"/>
     </row>
     <row r="14" spans="1:10" ht="33.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A14" s="7" t="s">
+      <c r="A14" s="2" t="s">
         <v>19</v>
       </c>
-      <c r="B14" s="8" t="s">
+      <c r="B14" s="3" t="s">
         <v>20</v>
       </c>
-      <c r="C14" s="7">
+      <c r="C14" s="2">
         <v>5</v>
       </c>
-      <c r="D14" s="7"/>
-      <c r="E14" s="7" t="s">
+      <c r="D14" t="s">
+        <v>125</v>
+      </c>
+      <c r="E14" s="2" t="s">
         <v>86</v>
       </c>
-      <c r="F14" s="7" t="s">
+      <c r="F14" s="2" t="s">
         <v>87</v>
       </c>
-      <c r="G14" s="7"/>
-      <c r="H14" s="7"/>
-      <c r="I14" s="7"/>
-      <c r="J14" s="7"/>
+      <c r="G14" s="2"/>
+      <c r="H14" s="2"/>
+      <c r="I14" s="2"/>
+      <c r="J14" s="2"/>
     </row>
     <row r="15" spans="1:10" ht="33.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A15" s="7" t="s">
+      <c r="A15" s="2" t="s">
         <v>21</v>
       </c>
-      <c r="B15" s="8" t="s">
+      <c r="B15" s="3" t="s">
         <v>22</v>
       </c>
-      <c r="C15" s="7">
-        <v>8</v>
-      </c>
-      <c r="D15" s="7"/>
-      <c r="E15" s="7" t="s">
+      <c r="C15" s="2">
+        <v>8</v>
+      </c>
+      <c r="D15" t="s">
+        <v>125</v>
+      </c>
+      <c r="E15" s="2" t="s">
         <v>86</v>
       </c>
-      <c r="F15" s="7" t="s">
+      <c r="F15" s="2" t="s">
         <v>87</v>
       </c>
-      <c r="G15" s="7"/>
-      <c r="H15" s="7"/>
-      <c r="I15" s="7"/>
-      <c r="J15" s="7"/>
+      <c r="G15" s="2"/>
+      <c r="H15" s="2"/>
+      <c r="I15" s="2"/>
+      <c r="J15" s="2"/>
     </row>
     <row r="16" spans="1:10" ht="33.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A16" s="7" t="s">
+      <c r="A16" s="2" t="s">
         <v>23</v>
       </c>
-      <c r="B16" s="8" t="s">
+      <c r="B16" s="3" t="s">
         <v>24</v>
       </c>
-      <c r="C16" s="7">
+      <c r="C16" s="2">
         <v>5</v>
       </c>
-      <c r="D16" s="7"/>
-      <c r="E16" s="7" t="s">
+      <c r="D16" t="s">
+        <v>125</v>
+      </c>
+      <c r="E16" s="2" t="s">
         <v>86</v>
       </c>
-      <c r="F16" s="7" t="s">
+      <c r="F16" s="2" t="s">
         <v>87</v>
       </c>
-      <c r="G16" s="7"/>
-      <c r="H16" s="7"/>
-      <c r="I16" s="7"/>
-      <c r="J16" s="7"/>
+      <c r="G16" s="2"/>
+      <c r="H16" s="2"/>
+      <c r="I16" s="2"/>
+      <c r="J16" s="2"/>
     </row>
     <row r="17" spans="1:10" ht="18" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A17" s="1" t="s">
+      <c r="A17" s="13" t="s">
         <v>88</v>
       </c>
-      <c r="B17" s="1"/>
-      <c r="C17" s="10">
+      <c r="B17" s="13"/>
+      <c r="C17" s="5">
         <f>SUM(C18:C20)</f>
         <v>21</v>
       </c>
-      <c r="D17" s="11"/>
-      <c r="E17" s="11"/>
-      <c r="F17" s="11"/>
-      <c r="G17" s="11"/>
-      <c r="H17" s="11"/>
-      <c r="I17" s="11"/>
-      <c r="J17" s="11"/>
+      <c r="D17" s="6"/>
+      <c r="E17" s="6"/>
+      <c r="F17" s="6"/>
+      <c r="G17" s="6"/>
+      <c r="H17" s="6"/>
+      <c r="I17" s="6"/>
+      <c r="J17" s="6"/>
     </row>
     <row r="18" spans="1:10" ht="33.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A18" s="7" t="s">
+      <c r="A18" s="2" t="s">
         <v>26</v>
       </c>
-      <c r="B18" s="8" t="s">
+      <c r="B18" s="3" t="s">
         <v>27</v>
       </c>
-      <c r="C18" s="7">
+      <c r="C18" s="2">
         <v>5</v>
       </c>
-      <c r="D18" s="7"/>
-      <c r="E18" s="7" t="s">
+      <c r="D18" t="s">
+        <v>137</v>
+      </c>
+      <c r="E18" s="2" t="s">
         <v>89</v>
       </c>
-      <c r="F18" s="7" t="s">
+      <c r="F18" s="2" t="s">
         <v>90</v>
       </c>
-      <c r="G18" s="7"/>
-      <c r="H18" s="7"/>
-      <c r="I18" s="7"/>
-      <c r="J18" s="7"/>
+      <c r="G18" s="2"/>
+      <c r="H18" s="2"/>
+      <c r="I18" s="2"/>
+      <c r="J18" s="2"/>
     </row>
     <row r="19" spans="1:10" ht="33.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A19" s="7" t="s">
+      <c r="A19" s="2" t="s">
         <v>28</v>
       </c>
-      <c r="B19" s="8" t="s">
+      <c r="B19" s="3" t="s">
         <v>29</v>
       </c>
-      <c r="C19" s="7">
-        <v>8</v>
-      </c>
-      <c r="D19" s="7"/>
-      <c r="E19" s="7" t="s">
+      <c r="C19" s="2">
+        <v>8</v>
+      </c>
+      <c r="D19" t="s">
+        <v>137</v>
+      </c>
+      <c r="E19" s="2" t="s">
         <v>89</v>
       </c>
-      <c r="F19" s="7" t="s">
+      <c r="F19" s="2" t="s">
         <v>90</v>
       </c>
-      <c r="G19" s="7"/>
-      <c r="H19" s="7"/>
-      <c r="I19" s="7"/>
-      <c r="J19" s="7"/>
+      <c r="G19" s="2"/>
+      <c r="H19" s="2"/>
+      <c r="I19" s="2"/>
+      <c r="J19" s="2"/>
     </row>
     <row r="20" spans="1:10" ht="33.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A20" s="7" t="s">
+      <c r="A20" s="2" t="s">
         <v>30</v>
       </c>
-      <c r="B20" s="8" t="s">
+      <c r="B20" s="3" t="s">
         <v>31</v>
       </c>
-      <c r="C20" s="7">
-        <v>8</v>
-      </c>
-      <c r="D20" s="7"/>
-      <c r="E20" s="7" t="s">
+      <c r="C20" s="2">
+        <v>8</v>
+      </c>
+      <c r="D20" t="s">
+        <v>137</v>
+      </c>
+      <c r="E20" s="2" t="s">
         <v>89</v>
       </c>
-      <c r="F20" s="7" t="s">
+      <c r="F20" s="2" t="s">
         <v>90</v>
       </c>
-      <c r="G20" s="7"/>
-      <c r="H20" s="7"/>
-      <c r="I20" s="7"/>
-      <c r="J20" s="7"/>
+      <c r="G20" s="2"/>
+      <c r="H20" s="2"/>
+      <c r="I20" s="2"/>
+      <c r="J20" s="2"/>
     </row>
     <row r="21" spans="1:10" ht="18" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A21" s="1" t="s">
+      <c r="A21" s="13" t="s">
         <v>91</v>
       </c>
-      <c r="B21" s="1"/>
-      <c r="C21" s="10">
+      <c r="B21" s="13"/>
+      <c r="C21" s="5">
         <f>SUM(C22:C24)</f>
         <v>16</v>
       </c>
-      <c r="D21" s="11"/>
-      <c r="E21" s="11"/>
-      <c r="F21" s="11"/>
-      <c r="G21" s="11"/>
-      <c r="H21" s="11"/>
-      <c r="I21" s="11"/>
-      <c r="J21" s="11"/>
+      <c r="D21" s="6"/>
+      <c r="E21" s="6"/>
+      <c r="F21" s="6"/>
+      <c r="G21" s="6"/>
+      <c r="H21" s="6"/>
+      <c r="I21" s="6"/>
+      <c r="J21" s="6"/>
     </row>
     <row r="22" spans="1:10" ht="33.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A22" s="7" t="s">
+      <c r="A22" s="2" t="s">
         <v>33</v>
       </c>
-      <c r="B22" s="8" t="s">
+      <c r="B22" s="3" t="s">
         <v>34</v>
       </c>
-      <c r="C22" s="7">
-        <v>8</v>
-      </c>
-      <c r="D22" s="7"/>
-      <c r="E22" s="7" t="s">
+      <c r="C22" s="2">
+        <v>8</v>
+      </c>
+      <c r="D22" t="s">
+        <v>131</v>
+      </c>
+      <c r="E22" s="2" t="s">
         <v>92</v>
       </c>
-      <c r="F22" s="7" t="s">
+      <c r="F22" s="2" t="s">
         <v>93</v>
       </c>
-      <c r="G22" s="7"/>
-      <c r="H22" s="7"/>
-      <c r="I22" s="7"/>
-      <c r="J22" s="7"/>
+      <c r="G22" s="2"/>
+      <c r="H22" s="2"/>
+      <c r="I22" s="2"/>
+      <c r="J22" s="2"/>
     </row>
     <row r="23" spans="1:10" ht="33.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A23" s="7" t="s">
+      <c r="A23" s="2" t="s">
         <v>35</v>
       </c>
-      <c r="B23" s="8" t="s">
+      <c r="B23" s="3" t="s">
         <v>36</v>
       </c>
-      <c r="C23" s="7">
+      <c r="C23" s="2">
         <v>5</v>
       </c>
-      <c r="D23" s="7"/>
-      <c r="E23" s="7" t="s">
+      <c r="D23" t="s">
+        <v>131</v>
+      </c>
+      <c r="E23" s="2" t="s">
         <v>92</v>
       </c>
-      <c r="F23" s="7" t="s">
+      <c r="F23" s="2" t="s">
         <v>93</v>
       </c>
-      <c r="G23" s="7"/>
-      <c r="H23" s="7"/>
-      <c r="I23" s="7"/>
-      <c r="J23" s="7"/>
+      <c r="G23" s="2"/>
+      <c r="H23" s="2"/>
+      <c r="I23" s="2"/>
+      <c r="J23" s="2"/>
     </row>
     <row r="24" spans="1:10" ht="33.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A24" s="7" t="s">
+      <c r="A24" s="2" t="s">
         <v>37</v>
       </c>
-      <c r="B24" s="8" t="s">
+      <c r="B24" s="3" t="s">
         <v>38</v>
       </c>
-      <c r="C24" s="7">
+      <c r="C24" s="2">
         <v>3</v>
       </c>
-      <c r="D24" s="7"/>
-      <c r="E24" s="7" t="s">
+      <c r="D24" t="s">
+        <v>131</v>
+      </c>
+      <c r="E24" s="2" t="s">
         <v>92</v>
       </c>
-      <c r="F24" s="7" t="s">
+      <c r="F24" s="2" t="s">
         <v>93</v>
       </c>
-      <c r="G24" s="7"/>
-      <c r="H24" s="7"/>
-      <c r="I24" s="7"/>
-      <c r="J24" s="7"/>
+      <c r="G24" s="2"/>
+      <c r="H24" s="2"/>
+      <c r="I24" s="2"/>
+      <c r="J24" s="2"/>
     </row>
     <row r="25" spans="1:10" ht="18" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A25" s="1" t="s">
+      <c r="A25" s="13" t="s">
         <v>94</v>
       </c>
-      <c r="B25" s="1"/>
-      <c r="C25" s="10">
+      <c r="B25" s="13"/>
+      <c r="C25" s="5">
         <f>SUM(C26:C27)</f>
         <v>13</v>
       </c>
-      <c r="D25" s="11"/>
-      <c r="E25" s="11"/>
-      <c r="F25" s="11"/>
-      <c r="G25" s="11"/>
-      <c r="H25" s="11"/>
-      <c r="I25" s="11"/>
-      <c r="J25" s="11"/>
+      <c r="D25" s="6"/>
+      <c r="E25" s="6"/>
+      <c r="F25" s="6"/>
+      <c r="G25" s="6"/>
+      <c r="H25" s="6"/>
+      <c r="I25" s="6"/>
+      <c r="J25" s="6"/>
     </row>
     <row r="26" spans="1:10" ht="33.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A26" s="7" t="s">
+      <c r="A26" s="2" t="s">
         <v>40</v>
       </c>
-      <c r="B26" s="8" t="s">
+      <c r="B26" s="3" t="s">
         <v>41</v>
       </c>
-      <c r="C26" s="7">
-        <v>8</v>
-      </c>
-      <c r="D26" s="7"/>
-      <c r="E26" s="7" t="s">
+      <c r="C26" s="2">
+        <v>8</v>
+      </c>
+      <c r="D26" t="s">
+        <v>134</v>
+      </c>
+      <c r="E26" s="2" t="s">
         <v>95</v>
       </c>
-      <c r="F26" s="7" t="s">
+      <c r="F26" s="2" t="s">
         <v>96</v>
       </c>
-      <c r="G26" s="7"/>
-      <c r="H26" s="7"/>
-      <c r="I26" s="7"/>
-      <c r="J26" s="7"/>
+      <c r="G26" s="2"/>
+      <c r="H26" s="2"/>
+      <c r="I26" s="2"/>
+      <c r="J26" s="2"/>
     </row>
     <row r="27" spans="1:10" ht="33.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A27" s="7" t="s">
+      <c r="A27" s="2" t="s">
         <v>42</v>
       </c>
-      <c r="B27" s="8" t="s">
+      <c r="B27" s="3" t="s">
         <v>43</v>
       </c>
-      <c r="C27" s="7">
+      <c r="C27" s="2">
         <v>5</v>
       </c>
-      <c r="D27" s="7"/>
-      <c r="E27" s="7" t="s">
+      <c r="D27" t="s">
+        <v>134</v>
+      </c>
+      <c r="E27" s="2" t="s">
         <v>95</v>
       </c>
-      <c r="F27" s="7" t="s">
+      <c r="F27" s="2" t="s">
         <v>96</v>
       </c>
-      <c r="G27" s="7"/>
-      <c r="H27" s="7"/>
-      <c r="I27" s="7"/>
-      <c r="J27" s="7"/>
+      <c r="G27" s="2"/>
+      <c r="H27" s="2"/>
+      <c r="I27" s="2"/>
+      <c r="J27" s="2"/>
     </row>
     <row r="28" spans="1:10" ht="18" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A28" s="1" t="s">
+      <c r="A28" s="13" t="s">
         <v>97</v>
       </c>
-      <c r="B28" s="1"/>
-      <c r="C28" s="10">
+      <c r="B28" s="13"/>
+      <c r="C28" s="5">
         <f>SUM(C29:C30)</f>
         <v>16</v>
       </c>
-      <c r="D28" s="11"/>
-      <c r="E28" s="11"/>
-      <c r="F28" s="11"/>
-      <c r="G28" s="11"/>
-      <c r="H28" s="11"/>
-      <c r="I28" s="11"/>
-      <c r="J28" s="11"/>
+      <c r="D28" s="6"/>
+      <c r="E28" s="6"/>
+      <c r="F28" s="6"/>
+      <c r="G28" s="6"/>
+      <c r="H28" s="6"/>
+      <c r="I28" s="6"/>
+      <c r="J28" s="6"/>
     </row>
     <row r="29" spans="1:10" ht="33.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A29" s="7" t="s">
+      <c r="A29" s="2" t="s">
         <v>44</v>
       </c>
-      <c r="B29" s="8" t="s">
+      <c r="B29" s="3" t="s">
         <v>45</v>
       </c>
-      <c r="C29" s="7">
-        <v>8</v>
-      </c>
-      <c r="D29" s="7"/>
-      <c r="E29" s="7" t="s">
+      <c r="C29" s="2">
+        <v>8</v>
+      </c>
+      <c r="D29" t="s">
+        <v>122</v>
+      </c>
+      <c r="E29" s="2" t="s">
         <v>98</v>
       </c>
-      <c r="F29" s="7" t="s">
+      <c r="F29" s="2" t="s">
         <v>99</v>
       </c>
-      <c r="G29" s="7"/>
-      <c r="H29" s="7"/>
-      <c r="I29" s="7"/>
-      <c r="J29" s="7"/>
+      <c r="G29" s="2"/>
+      <c r="H29" s="2"/>
+      <c r="I29" s="2"/>
+      <c r="J29" s="2"/>
     </row>
     <row r="30" spans="1:10" ht="33.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A30" s="7" t="s">
+      <c r="A30" s="2" t="s">
         <v>46</v>
       </c>
-      <c r="B30" s="8" t="s">
+      <c r="B30" s="3" t="s">
         <v>47</v>
       </c>
-      <c r="C30" s="7">
-        <v>8</v>
-      </c>
-      <c r="D30" s="7"/>
-      <c r="E30" s="7" t="s">
+      <c r="C30" s="2">
+        <v>8</v>
+      </c>
+      <c r="D30" t="s">
+        <v>122</v>
+      </c>
+      <c r="E30" s="2" t="s">
         <v>98</v>
       </c>
-      <c r="F30" s="7" t="s">
+      <c r="F30" s="2" t="s">
         <v>99</v>
       </c>
-      <c r="G30" s="7"/>
-      <c r="H30" s="7"/>
-      <c r="I30" s="7"/>
-      <c r="J30" s="7"/>
+      <c r="G30" s="2"/>
+      <c r="H30" s="2"/>
+      <c r="I30" s="2"/>
+      <c r="J30" s="2"/>
     </row>
     <row r="31" spans="1:10" ht="18" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A31" s="1" t="s">
+      <c r="A31" s="13" t="s">
         <v>100</v>
       </c>
-      <c r="B31" s="1"/>
-      <c r="C31" s="10">
+      <c r="B31" s="13"/>
+      <c r="C31" s="5">
         <f>SUM(C32:C33)</f>
         <v>13</v>
       </c>
-      <c r="D31" s="11"/>
-      <c r="E31" s="11"/>
-      <c r="F31" s="11"/>
-      <c r="G31" s="11"/>
-      <c r="H31" s="11"/>
-      <c r="I31" s="11"/>
-      <c r="J31" s="11"/>
+      <c r="D31" s="6"/>
+      <c r="E31" s="6"/>
+      <c r="F31" s="6"/>
+      <c r="G31" s="6"/>
+      <c r="H31" s="6"/>
+      <c r="I31" s="6"/>
+      <c r="J31" s="6"/>
     </row>
     <row r="32" spans="1:10" ht="33.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A32" s="7" t="s">
+      <c r="A32" s="2" t="s">
         <v>49</v>
       </c>
-      <c r="B32" s="8" t="s">
+      <c r="B32" s="3" t="s">
         <v>50</v>
       </c>
-      <c r="C32" s="7">
-        <v>8</v>
-      </c>
-      <c r="D32" s="7"/>
-      <c r="E32" s="7" t="s">
+      <c r="C32" s="2">
+        <v>8</v>
+      </c>
+      <c r="D32" t="s">
+        <v>125</v>
+      </c>
+      <c r="E32" s="2" t="s">
         <v>101</v>
       </c>
-      <c r="F32" s="7" t="s">
+      <c r="F32" s="2" t="s">
         <v>102</v>
       </c>
-      <c r="G32" s="7"/>
-      <c r="H32" s="7"/>
-      <c r="I32" s="7"/>
-      <c r="J32" s="7"/>
+      <c r="G32" s="2"/>
+      <c r="H32" s="2"/>
+      <c r="I32" s="2"/>
+      <c r="J32" s="2"/>
     </row>
     <row r="33" spans="1:10" ht="33.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A33" s="7" t="s">
+      <c r="A33" s="2" t="s">
         <v>51</v>
       </c>
-      <c r="B33" s="8" t="s">
+      <c r="B33" s="3" t="s">
         <v>52</v>
       </c>
-      <c r="C33" s="7">
+      <c r="C33" s="2">
         <v>5</v>
       </c>
-      <c r="D33" s="7"/>
-      <c r="E33" s="7" t="s">
+      <c r="D33" t="s">
+        <v>125</v>
+      </c>
+      <c r="E33" s="2" t="s">
         <v>101</v>
       </c>
-      <c r="F33" s="7" t="s">
+      <c r="F33" s="2" t="s">
         <v>102</v>
       </c>
-      <c r="G33" s="7"/>
-      <c r="H33" s="7"/>
-      <c r="I33" s="7"/>
-      <c r="J33" s="7"/>
+      <c r="G33" s="2"/>
+      <c r="H33" s="2"/>
+      <c r="I33" s="2"/>
+      <c r="J33" s="2"/>
     </row>
     <row r="34" spans="1:10" ht="18" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A34" s="1" t="s">
+      <c r="A34" s="13" t="s">
         <v>103</v>
       </c>
-      <c r="B34" s="1"/>
-      <c r="C34" s="10">
+      <c r="B34" s="13"/>
+      <c r="C34" s="5">
         <f>SUM(C35:C36)</f>
         <v>18</v>
       </c>
-      <c r="D34" s="11"/>
-      <c r="E34" s="11"/>
-      <c r="F34" s="11"/>
-      <c r="G34" s="11"/>
-      <c r="H34" s="11"/>
-      <c r="I34" s="11"/>
-      <c r="J34" s="11"/>
+      <c r="D34" s="6"/>
+      <c r="E34" s="6"/>
+      <c r="F34" s="6"/>
+      <c r="G34" s="6"/>
+      <c r="H34" s="6"/>
+      <c r="I34" s="6"/>
+      <c r="J34" s="6"/>
     </row>
     <row r="35" spans="1:10" ht="33.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A35" s="7" t="s">
+      <c r="A35" s="2" t="s">
         <v>53</v>
       </c>
-      <c r="B35" s="8" t="s">
+      <c r="B35" s="3" t="s">
         <v>54</v>
       </c>
-      <c r="C35" s="7">
+      <c r="C35" s="2">
         <v>5</v>
       </c>
-      <c r="D35" s="7"/>
-      <c r="E35" s="7" t="s">
+      <c r="D35" t="s">
+        <v>137</v>
+      </c>
+      <c r="E35" s="2" t="s">
         <v>104</v>
       </c>
-      <c r="F35" s="7" t="s">
+      <c r="F35" s="2" t="s">
         <v>105</v>
       </c>
-      <c r="G35" s="7"/>
-      <c r="H35" s="7"/>
-      <c r="I35" s="7"/>
-      <c r="J35" s="7"/>
+      <c r="G35" s="2"/>
+      <c r="H35" s="2"/>
+      <c r="I35" s="2"/>
+      <c r="J35" s="2"/>
     </row>
     <row r="36" spans="1:10" ht="33.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A36" s="7" t="s">
+      <c r="A36" s="2" t="s">
         <v>55</v>
       </c>
-      <c r="B36" s="8" t="s">
+      <c r="B36" s="3" t="s">
         <v>56</v>
       </c>
-      <c r="C36" s="7">
+      <c r="C36" s="2">
         <v>13</v>
       </c>
-      <c r="D36" s="7"/>
-      <c r="E36" s="7" t="s">
+      <c r="D36" t="s">
+        <v>137</v>
+      </c>
+      <c r="E36" s="2" t="s">
         <v>104</v>
       </c>
-      <c r="F36" s="7" t="s">
+      <c r="F36" s="2" t="s">
         <v>105</v>
       </c>
-      <c r="G36" s="7"/>
-      <c r="H36" s="7"/>
-      <c r="I36" s="7"/>
-      <c r="J36" s="7"/>
+      <c r="G36" s="2"/>
+      <c r="H36" s="2"/>
+      <c r="I36" s="2"/>
+      <c r="J36" s="2"/>
     </row>
     <row r="37" spans="1:10" ht="18" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A37" s="1" t="s">
+      <c r="A37" s="13" t="s">
         <v>106</v>
       </c>
-      <c r="B37" s="1"/>
-      <c r="C37" s="10">
+      <c r="B37" s="13"/>
+      <c r="C37" s="5">
         <f>SUM(C38:C40)</f>
         <v>16</v>
       </c>
-      <c r="D37" s="11"/>
-      <c r="E37" s="11"/>
-      <c r="F37" s="11"/>
-      <c r="G37" s="11"/>
-      <c r="H37" s="11"/>
-      <c r="I37" s="11"/>
-      <c r="J37" s="11"/>
+      <c r="D37" s="6"/>
+      <c r="E37" s="6"/>
+      <c r="F37" s="6"/>
+      <c r="G37" s="6"/>
+      <c r="H37" s="6"/>
+      <c r="I37" s="6"/>
+      <c r="J37" s="6"/>
     </row>
     <row r="38" spans="1:10" ht="33.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A38" s="7" t="s">
+      <c r="A38" s="2" t="s">
         <v>58</v>
       </c>
-      <c r="B38" s="8" t="s">
+      <c r="B38" s="3" t="s">
         <v>59</v>
       </c>
-      <c r="C38" s="7">
-        <v>8</v>
-      </c>
-      <c r="D38" s="7"/>
-      <c r="E38" s="7" t="s">
+      <c r="C38" s="2">
+        <v>8</v>
+      </c>
+      <c r="D38" t="s">
+        <v>131</v>
+      </c>
+      <c r="E38" s="2" t="s">
         <v>107</v>
       </c>
-      <c r="F38" s="7" t="s">
+      <c r="F38" s="2" t="s">
         <v>108</v>
       </c>
-      <c r="G38" s="7"/>
-      <c r="H38" s="7"/>
-      <c r="I38" s="7"/>
-      <c r="J38" s="7"/>
+      <c r="G38" s="2"/>
+      <c r="H38" s="2"/>
+      <c r="I38" s="2"/>
+      <c r="J38" s="2"/>
     </row>
     <row r="39" spans="1:10" ht="33.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A39" s="7" t="s">
+      <c r="A39" s="2" t="s">
         <v>60</v>
       </c>
-      <c r="B39" s="8" t="s">
+      <c r="B39" s="3" t="s">
         <v>61</v>
       </c>
-      <c r="C39" s="7">
+      <c r="C39" s="2">
         <v>3</v>
       </c>
-      <c r="D39" s="7"/>
-      <c r="E39" s="7" t="s">
+      <c r="D39" t="s">
+        <v>131</v>
+      </c>
+      <c r="E39" s="2" t="s">
         <v>107</v>
       </c>
-      <c r="F39" s="7" t="s">
+      <c r="F39" s="2" t="s">
         <v>108</v>
       </c>
-      <c r="G39" s="7"/>
-      <c r="H39" s="7"/>
-      <c r="I39" s="7"/>
-      <c r="J39" s="7"/>
+      <c r="G39" s="2"/>
+      <c r="H39" s="2"/>
+      <c r="I39" s="2"/>
+      <c r="J39" s="2"/>
     </row>
     <row r="40" spans="1:10" ht="33.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A40" s="7" t="s">
+      <c r="A40" s="2" t="s">
         <v>62</v>
       </c>
-      <c r="B40" s="8" t="s">
+      <c r="B40" s="3" t="s">
         <v>63</v>
       </c>
-      <c r="C40" s="7">
+      <c r="C40" s="2">
         <v>5</v>
       </c>
-      <c r="D40" s="7"/>
-      <c r="E40" s="7" t="s">
+      <c r="D40" t="s">
+        <v>131</v>
+      </c>
+      <c r="E40" s="2" t="s">
         <v>107</v>
       </c>
-      <c r="F40" s="7" t="s">
+      <c r="F40" s="2" t="s">
         <v>108</v>
       </c>
-      <c r="G40" s="7"/>
-      <c r="H40" s="7"/>
-      <c r="I40" s="7"/>
-      <c r="J40" s="7"/>
+      <c r="G40" s="2"/>
+      <c r="H40" s="2"/>
+      <c r="I40" s="2"/>
+      <c r="J40" s="2"/>
     </row>
     <row r="41" spans="1:10" ht="18" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A41" s="1" t="s">
+      <c r="A41" s="13" t="s">
         <v>109</v>
       </c>
-      <c r="B41" s="1"/>
-      <c r="C41" s="10">
+      <c r="B41" s="13"/>
+      <c r="C41" s="5">
         <f>SUM(C42:C43)</f>
         <v>16</v>
       </c>
-      <c r="D41" s="11"/>
-      <c r="E41" s="11"/>
-      <c r="F41" s="11"/>
-      <c r="G41" s="11"/>
-      <c r="H41" s="11"/>
-      <c r="I41" s="11"/>
-      <c r="J41" s="11"/>
+      <c r="D41" s="6"/>
+      <c r="E41" s="6"/>
+      <c r="F41" s="6"/>
+      <c r="G41" s="6"/>
+      <c r="H41" s="6"/>
+      <c r="I41" s="6"/>
+      <c r="J41" s="6"/>
     </row>
     <row r="42" spans="1:10" ht="33.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A42" s="7" t="s">
+      <c r="A42" s="2" t="s">
         <v>65</v>
       </c>
-      <c r="B42" s="8" t="s">
+      <c r="B42" s="3" t="s">
         <v>66</v>
       </c>
-      <c r="C42" s="7">
-        <v>8</v>
-      </c>
-      <c r="D42" s="7"/>
-      <c r="E42" s="7" t="s">
+      <c r="C42" s="2">
+        <v>8</v>
+      </c>
+      <c r="D42" t="s">
+        <v>134</v>
+      </c>
+      <c r="E42" s="2" t="s">
         <v>110</v>
       </c>
-      <c r="F42" s="7" t="s">
+      <c r="F42" s="2" t="s">
         <v>111</v>
       </c>
-      <c r="G42" s="7"/>
-      <c r="H42" s="7"/>
-      <c r="I42" s="7"/>
-      <c r="J42" s="7"/>
+      <c r="G42" s="2"/>
+      <c r="H42" s="2"/>
+      <c r="I42" s="2"/>
+      <c r="J42" s="2"/>
     </row>
     <row r="43" spans="1:10" ht="33.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A43" s="7" t="s">
+      <c r="A43" s="2" t="s">
         <v>67</v>
       </c>
-      <c r="B43" s="8" t="s">
+      <c r="B43" s="3" t="s">
         <v>68</v>
       </c>
-      <c r="C43" s="7">
-        <v>8</v>
-      </c>
-      <c r="D43" s="7"/>
-      <c r="E43" s="7" t="s">
+      <c r="C43" s="2">
+        <v>8</v>
+      </c>
+      <c r="D43" t="s">
+        <v>134</v>
+      </c>
+      <c r="E43" s="2" t="s">
         <v>110</v>
       </c>
-      <c r="F43" s="7" t="s">
+      <c r="F43" s="2" t="s">
         <v>111</v>
       </c>
-      <c r="G43" s="7"/>
-      <c r="H43" s="7"/>
-      <c r="I43" s="7"/>
-      <c r="J43" s="7"/>
+      <c r="G43" s="2"/>
+      <c r="H43" s="2"/>
+      <c r="I43" s="2"/>
+      <c r="J43" s="2"/>
     </row>
     <row r="44" spans="1:10" ht="18" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A44" s="3" t="s">
+      <c r="A44" s="14" t="s">
         <v>112</v>
       </c>
-      <c r="B44" s="3"/>
-      <c r="C44" s="9">
+      <c r="B44" s="14"/>
+      <c r="C44" s="4">
         <f>SUM(C6:C8)+SUM(C10:C12)+SUM(C14:C16)+SUM(C18:C20)+SUM(C22:C24)+SUM(C26:C27)+SUM(C29:C30)+SUM(C32:C33)+SUM(C35:C36)+SUM(C38:C40)+SUM(C42:C43)</f>
         <v>186</v>
       </c>
     </row>
   </sheetData>
   <mergeCells count="14">
+    <mergeCell ref="A1:J1"/>
+    <mergeCell ref="A2:J2"/>
+    <mergeCell ref="A5:B5"/>
+    <mergeCell ref="A9:B9"/>
+    <mergeCell ref="A13:B13"/>
     <mergeCell ref="A34:B34"/>
     <mergeCell ref="A37:B37"/>
     <mergeCell ref="A41:B41"/>
@@ -2212,11 +2276,6 @@
     <mergeCell ref="A25:B25"/>
     <mergeCell ref="A28:B28"/>
     <mergeCell ref="A31:B31"/>
-    <mergeCell ref="A1:J1"/>
-    <mergeCell ref="A2:J2"/>
-    <mergeCell ref="A5:B5"/>
-    <mergeCell ref="A9:B9"/>
-    <mergeCell ref="A13:B13"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.511811023622047" footer="0.511811023622047"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300"/>
@@ -2229,249 +2288,249 @@
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <sheetData>
     <row r="2" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A2" s="12" t="s">
+      <c r="A2" s="7" t="s">
         <v>113</v>
       </c>
     </row>
     <row r="3" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A3" s="13" t="s">
+      <c r="A3" s="18" t="s">
         <v>114</v>
       </c>
-      <c r="B3" s="14"/>
-      <c r="C3" s="14"/>
-      <c r="D3" s="14"/>
-      <c r="E3" s="14"/>
-      <c r="F3" s="14"/>
-      <c r="G3" s="14"/>
-      <c r="H3" s="14"/>
-      <c r="I3" s="14"/>
-      <c r="J3" s="14"/>
-      <c r="K3" s="14"/>
-      <c r="L3" s="14"/>
+      <c r="B3" s="19"/>
+      <c r="C3" s="19"/>
+      <c r="D3" s="19"/>
+      <c r="E3" s="19"/>
+      <c r="F3" s="19"/>
+      <c r="G3" s="19"/>
+      <c r="H3" s="19"/>
+      <c r="I3" s="19"/>
+      <c r="J3" s="19"/>
+      <c r="K3" s="19"/>
+      <c r="L3" s="19"/>
     </row>
     <row r="4" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A4" s="14"/>
-      <c r="B4" s="14"/>
-      <c r="C4" s="14"/>
-      <c r="D4" s="14"/>
-      <c r="E4" s="14"/>
-      <c r="F4" s="14"/>
-      <c r="G4" s="14"/>
-      <c r="H4" s="14"/>
-      <c r="I4" s="14"/>
-      <c r="J4" s="14"/>
-      <c r="K4" s="14"/>
-      <c r="L4" s="14"/>
+      <c r="A4" s="19"/>
+      <c r="B4" s="19"/>
+      <c r="C4" s="19"/>
+      <c r="D4" s="19"/>
+      <c r="E4" s="19"/>
+      <c r="F4" s="19"/>
+      <c r="G4" s="19"/>
+      <c r="H4" s="19"/>
+      <c r="I4" s="19"/>
+      <c r="J4" s="19"/>
+      <c r="K4" s="19"/>
+      <c r="L4" s="19"/>
     </row>
     <row r="5" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A5" s="14"/>
-      <c r="B5" s="14"/>
-      <c r="C5" s="14"/>
-      <c r="D5" s="14"/>
-      <c r="E5" s="14"/>
-      <c r="F5" s="14"/>
-      <c r="G5" s="14"/>
-      <c r="H5" s="14"/>
-      <c r="I5" s="14"/>
-      <c r="J5" s="14"/>
-      <c r="K5" s="14"/>
-      <c r="L5" s="14"/>
+      <c r="A5" s="19"/>
+      <c r="B5" s="19"/>
+      <c r="C5" s="19"/>
+      <c r="D5" s="19"/>
+      <c r="E5" s="19"/>
+      <c r="F5" s="19"/>
+      <c r="G5" s="19"/>
+      <c r="H5" s="19"/>
+      <c r="I5" s="19"/>
+      <c r="J5" s="19"/>
+      <c r="K5" s="19"/>
+      <c r="L5" s="19"/>
     </row>
     <row r="6" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A6" s="14"/>
-      <c r="B6" s="14"/>
-      <c r="C6" s="14"/>
-      <c r="D6" s="14"/>
-      <c r="E6" s="14"/>
-      <c r="F6" s="14"/>
-      <c r="G6" s="14"/>
-      <c r="H6" s="14"/>
-      <c r="I6" s="14"/>
-      <c r="J6" s="14"/>
-      <c r="K6" s="14"/>
-      <c r="L6" s="14"/>
+      <c r="A6" s="19"/>
+      <c r="B6" s="19"/>
+      <c r="C6" s="19"/>
+      <c r="D6" s="19"/>
+      <c r="E6" s="19"/>
+      <c r="F6" s="19"/>
+      <c r="G6" s="19"/>
+      <c r="H6" s="19"/>
+      <c r="I6" s="19"/>
+      <c r="J6" s="19"/>
+      <c r="K6" s="19"/>
+      <c r="L6" s="19"/>
     </row>
     <row r="7" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A7" s="14"/>
-      <c r="B7" s="14"/>
-      <c r="C7" s="14"/>
-      <c r="D7" s="14"/>
-      <c r="E7" s="14"/>
-      <c r="F7" s="14"/>
-      <c r="G7" s="14"/>
-      <c r="H7" s="14"/>
-      <c r="I7" s="14"/>
-      <c r="J7" s="14"/>
-      <c r="K7" s="14"/>
-      <c r="L7" s="14"/>
+      <c r="A7" s="19"/>
+      <c r="B7" s="19"/>
+      <c r="C7" s="19"/>
+      <c r="D7" s="19"/>
+      <c r="E7" s="19"/>
+      <c r="F7" s="19"/>
+      <c r="G7" s="19"/>
+      <c r="H7" s="19"/>
+      <c r="I7" s="19"/>
+      <c r="J7" s="19"/>
+      <c r="K7" s="19"/>
+      <c r="L7" s="19"/>
     </row>
     <row r="8" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A8" s="14"/>
-      <c r="B8" s="14"/>
-      <c r="C8" s="14"/>
-      <c r="D8" s="14"/>
-      <c r="E8" s="14"/>
-      <c r="F8" s="14"/>
-      <c r="G8" s="14"/>
-      <c r="H8" s="14"/>
-      <c r="I8" s="14"/>
-      <c r="J8" s="14"/>
-      <c r="K8" s="14"/>
-      <c r="L8" s="14"/>
+      <c r="A8" s="19"/>
+      <c r="B8" s="19"/>
+      <c r="C8" s="19"/>
+      <c r="D8" s="19"/>
+      <c r="E8" s="19"/>
+      <c r="F8" s="19"/>
+      <c r="G8" s="19"/>
+      <c r="H8" s="19"/>
+      <c r="I8" s="19"/>
+      <c r="J8" s="19"/>
+      <c r="K8" s="19"/>
+      <c r="L8" s="19"/>
     </row>
     <row r="9" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A9" s="14"/>
-      <c r="B9" s="14"/>
-      <c r="C9" s="14"/>
-      <c r="D9" s="14"/>
-      <c r="E9" s="14"/>
-      <c r="F9" s="14"/>
-      <c r="G9" s="14"/>
-      <c r="H9" s="14"/>
-      <c r="I9" s="14"/>
-      <c r="J9" s="14"/>
-      <c r="K9" s="14"/>
-      <c r="L9" s="14"/>
+      <c r="A9" s="19"/>
+      <c r="B9" s="19"/>
+      <c r="C9" s="19"/>
+      <c r="D9" s="19"/>
+      <c r="E9" s="19"/>
+      <c r="F9" s="19"/>
+      <c r="G9" s="19"/>
+      <c r="H9" s="19"/>
+      <c r="I9" s="19"/>
+      <c r="J9" s="19"/>
+      <c r="K9" s="19"/>
+      <c r="L9" s="19"/>
     </row>
     <row r="10" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A10" s="14"/>
-      <c r="B10" s="14"/>
-      <c r="C10" s="14"/>
-      <c r="D10" s="14"/>
-      <c r="E10" s="14"/>
-      <c r="F10" s="14"/>
-      <c r="G10" s="14"/>
-      <c r="H10" s="14"/>
-      <c r="I10" s="14"/>
-      <c r="J10" s="14"/>
-      <c r="K10" s="14"/>
-      <c r="L10" s="14"/>
+      <c r="A10" s="19"/>
+      <c r="B10" s="19"/>
+      <c r="C10" s="19"/>
+      <c r="D10" s="19"/>
+      <c r="E10" s="19"/>
+      <c r="F10" s="19"/>
+      <c r="G10" s="19"/>
+      <c r="H10" s="19"/>
+      <c r="I10" s="19"/>
+      <c r="J10" s="19"/>
+      <c r="K10" s="19"/>
+      <c r="L10" s="19"/>
     </row>
     <row r="11" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A11" s="14"/>
-      <c r="B11" s="14"/>
-      <c r="C11" s="14"/>
-      <c r="D11" s="14"/>
-      <c r="E11" s="14"/>
-      <c r="F11" s="14"/>
-      <c r="G11" s="14"/>
-      <c r="H11" s="14"/>
-      <c r="I11" s="14"/>
-      <c r="J11" s="14"/>
-      <c r="K11" s="14"/>
-      <c r="L11" s="14"/>
+      <c r="A11" s="19"/>
+      <c r="B11" s="19"/>
+      <c r="C11" s="19"/>
+      <c r="D11" s="19"/>
+      <c r="E11" s="19"/>
+      <c r="F11" s="19"/>
+      <c r="G11" s="19"/>
+      <c r="H11" s="19"/>
+      <c r="I11" s="19"/>
+      <c r="J11" s="19"/>
+      <c r="K11" s="19"/>
+      <c r="L11" s="19"/>
     </row>
     <row r="12" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A12" s="14"/>
-      <c r="B12" s="14"/>
-      <c r="C12" s="14"/>
-      <c r="D12" s="14"/>
-      <c r="E12" s="14"/>
-      <c r="F12" s="14"/>
-      <c r="G12" s="14"/>
-      <c r="H12" s="14"/>
-      <c r="I12" s="14"/>
-      <c r="J12" s="14"/>
-      <c r="K12" s="14"/>
-      <c r="L12" s="14"/>
+      <c r="A12" s="19"/>
+      <c r="B12" s="19"/>
+      <c r="C12" s="19"/>
+      <c r="D12" s="19"/>
+      <c r="E12" s="19"/>
+      <c r="F12" s="19"/>
+      <c r="G12" s="19"/>
+      <c r="H12" s="19"/>
+      <c r="I12" s="19"/>
+      <c r="J12" s="19"/>
+      <c r="K12" s="19"/>
+      <c r="L12" s="19"/>
     </row>
     <row r="13" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A13" s="14"/>
-      <c r="B13" s="14"/>
-      <c r="C13" s="14"/>
-      <c r="D13" s="14"/>
-      <c r="E13" s="14"/>
-      <c r="F13" s="14"/>
-      <c r="G13" s="14"/>
-      <c r="H13" s="14"/>
-      <c r="I13" s="14"/>
-      <c r="J13" s="14"/>
-      <c r="K13" s="14"/>
-      <c r="L13" s="14"/>
+      <c r="A13" s="19"/>
+      <c r="B13" s="19"/>
+      <c r="C13" s="19"/>
+      <c r="D13" s="19"/>
+      <c r="E13" s="19"/>
+      <c r="F13" s="19"/>
+      <c r="G13" s="19"/>
+      <c r="H13" s="19"/>
+      <c r="I13" s="19"/>
+      <c r="J13" s="19"/>
+      <c r="K13" s="19"/>
+      <c r="L13" s="19"/>
     </row>
     <row r="14" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A14" s="14"/>
-      <c r="B14" s="14"/>
-      <c r="C14" s="14"/>
-      <c r="D14" s="14"/>
-      <c r="E14" s="14"/>
-      <c r="F14" s="14"/>
-      <c r="G14" s="14"/>
-      <c r="H14" s="14"/>
-      <c r="I14" s="14"/>
-      <c r="J14" s="14"/>
-      <c r="K14" s="14"/>
-      <c r="L14" s="14"/>
+      <c r="A14" s="19"/>
+      <c r="B14" s="19"/>
+      <c r="C14" s="19"/>
+      <c r="D14" s="19"/>
+      <c r="E14" s="19"/>
+      <c r="F14" s="19"/>
+      <c r="G14" s="19"/>
+      <c r="H14" s="19"/>
+      <c r="I14" s="19"/>
+      <c r="J14" s="19"/>
+      <c r="K14" s="19"/>
+      <c r="L14" s="19"/>
     </row>
     <row r="15" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A15" s="14"/>
-      <c r="B15" s="14"/>
-      <c r="C15" s="14"/>
-      <c r="D15" s="14"/>
-      <c r="E15" s="14"/>
-      <c r="F15" s="14"/>
-      <c r="G15" s="14"/>
-      <c r="H15" s="14"/>
-      <c r="I15" s="14"/>
-      <c r="J15" s="14"/>
-      <c r="K15" s="14"/>
-      <c r="L15" s="14"/>
+      <c r="A15" s="19"/>
+      <c r="B15" s="19"/>
+      <c r="C15" s="19"/>
+      <c r="D15" s="19"/>
+      <c r="E15" s="19"/>
+      <c r="F15" s="19"/>
+      <c r="G15" s="19"/>
+      <c r="H15" s="19"/>
+      <c r="I15" s="19"/>
+      <c r="J15" s="19"/>
+      <c r="K15" s="19"/>
+      <c r="L15" s="19"/>
     </row>
     <row r="16" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A16" s="14"/>
-      <c r="B16" s="14"/>
-      <c r="C16" s="14"/>
-      <c r="D16" s="14"/>
-      <c r="E16" s="14"/>
-      <c r="F16" s="14"/>
-      <c r="G16" s="14"/>
-      <c r="H16" s="14"/>
-      <c r="I16" s="14"/>
-      <c r="J16" s="14"/>
-      <c r="K16" s="14"/>
-      <c r="L16" s="14"/>
+      <c r="A16" s="19"/>
+      <c r="B16" s="19"/>
+      <c r="C16" s="19"/>
+      <c r="D16" s="19"/>
+      <c r="E16" s="19"/>
+      <c r="F16" s="19"/>
+      <c r="G16" s="19"/>
+      <c r="H16" s="19"/>
+      <c r="I16" s="19"/>
+      <c r="J16" s="19"/>
+      <c r="K16" s="19"/>
+      <c r="L16" s="19"/>
     </row>
     <row r="17" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A17" s="14"/>
-      <c r="B17" s="14"/>
-      <c r="C17" s="14"/>
-      <c r="D17" s="14"/>
-      <c r="E17" s="14"/>
-      <c r="F17" s="14"/>
-      <c r="G17" s="14"/>
-      <c r="H17" s="14"/>
-      <c r="I17" s="14"/>
-      <c r="J17" s="14"/>
-      <c r="K17" s="14"/>
-      <c r="L17" s="14"/>
+      <c r="A17" s="19"/>
+      <c r="B17" s="19"/>
+      <c r="C17" s="19"/>
+      <c r="D17" s="19"/>
+      <c r="E17" s="19"/>
+      <c r="F17" s="19"/>
+      <c r="G17" s="19"/>
+      <c r="H17" s="19"/>
+      <c r="I17" s="19"/>
+      <c r="J17" s="19"/>
+      <c r="K17" s="19"/>
+      <c r="L17" s="19"/>
     </row>
     <row r="18" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A18" s="14"/>
-      <c r="B18" s="14"/>
-      <c r="C18" s="14"/>
-      <c r="D18" s="14"/>
-      <c r="E18" s="14"/>
-      <c r="F18" s="14"/>
-      <c r="G18" s="14"/>
-      <c r="H18" s="14"/>
-      <c r="I18" s="14"/>
-      <c r="J18" s="14"/>
-      <c r="K18" s="14"/>
-      <c r="L18" s="14"/>
+      <c r="A18" s="19"/>
+      <c r="B18" s="19"/>
+      <c r="C18" s="19"/>
+      <c r="D18" s="19"/>
+      <c r="E18" s="19"/>
+      <c r="F18" s="19"/>
+      <c r="G18" s="19"/>
+      <c r="H18" s="19"/>
+      <c r="I18" s="19"/>
+      <c r="J18" s="19"/>
+      <c r="K18" s="19"/>
+      <c r="L18" s="19"/>
     </row>
     <row r="19" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A19" s="14"/>
-      <c r="B19" s="14"/>
-      <c r="C19" s="14"/>
-      <c r="D19" s="14"/>
-      <c r="E19" s="14"/>
-      <c r="F19" s="14"/>
-      <c r="G19" s="14"/>
-      <c r="H19" s="14"/>
-      <c r="I19" s="14"/>
-      <c r="J19" s="14"/>
-      <c r="K19" s="14"/>
-      <c r="L19" s="14"/>
+      <c r="A19" s="19"/>
+      <c r="B19" s="19"/>
+      <c r="C19" s="19"/>
+      <c r="D19" s="19"/>
+      <c r="E19" s="19"/>
+      <c r="F19" s="19"/>
+      <c r="G19" s="19"/>
+      <c r="H19" s="19"/>
+      <c r="I19" s="19"/>
+      <c r="J19" s="19"/>
+      <c r="K19" s="19"/>
+      <c r="L19" s="19"/>
     </row>
   </sheetData>
   <mergeCells count="1">
@@ -2492,134 +2551,134 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A1" s="15" t="s">
+      <c r="A1" s="20" t="s">
         <v>115</v>
       </c>
-      <c r="B1" s="15"/>
-      <c r="C1" s="15"/>
-      <c r="D1" s="15"/>
-      <c r="E1" s="15"/>
-      <c r="F1" s="15"/>
+      <c r="B1" s="20"/>
+      <c r="C1" s="20"/>
+      <c r="D1" s="20"/>
+      <c r="E1" s="20"/>
+      <c r="F1" s="20"/>
     </row>
     <row r="3" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A3" s="16" t="s">
+      <c r="A3" s="8" t="s">
         <v>116</v>
       </c>
-      <c r="B3" s="16" t="s">
+      <c r="B3" s="8" t="s">
         <v>117</v>
       </c>
-      <c r="C3" s="16" t="s">
+      <c r="C3" s="8" t="s">
         <v>118</v>
       </c>
-      <c r="D3" s="16" t="s">
+      <c r="D3" s="8" t="s">
         <v>119</v>
       </c>
-      <c r="E3" s="16" t="s">
+      <c r="E3" s="8" t="s">
         <v>120</v>
       </c>
-      <c r="F3" s="16" t="s">
+      <c r="F3" s="8" t="s">
         <v>121</v>
       </c>
     </row>
     <row r="4" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A4" s="17">
+      <c r="A4" s="9">
         <v>1</v>
       </c>
-      <c r="B4" s="17" t="s">
+      <c r="B4" s="9" t="s">
         <v>122</v>
       </c>
-      <c r="C4" s="17" t="s">
+      <c r="C4" s="9" t="s">
         <v>123</v>
       </c>
       <c r="D4" t="s">
         <v>124</v>
       </c>
-      <c r="E4" s="18"/>
-      <c r="F4" s="17"/>
+      <c r="E4" s="10"/>
+      <c r="F4" s="9"/>
     </row>
     <row r="5" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A5" s="17">
+      <c r="A5" s="9">
         <v>2</v>
       </c>
-      <c r="B5" s="17" t="s">
+      <c r="B5" s="9" t="s">
         <v>125</v>
       </c>
-      <c r="C5" s="17" t="s">
+      <c r="C5" s="9" t="s">
         <v>126</v>
       </c>
       <c r="D5" t="s">
         <v>127</v>
       </c>
-      <c r="E5" s="18"/>
-      <c r="F5" s="17"/>
+      <c r="E5" s="10"/>
+      <c r="F5" s="9"/>
     </row>
     <row r="6" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A6" s="17">
+      <c r="A6" s="9">
         <v>3</v>
       </c>
-      <c r="B6" s="17" t="s">
+      <c r="B6" s="9" t="s">
         <v>128</v>
       </c>
-      <c r="C6" s="17" t="s">
+      <c r="C6" s="9" t="s">
         <v>129</v>
       </c>
       <c r="D6" t="s">
         <v>130</v>
       </c>
-      <c r="E6" s="18"/>
-      <c r="F6" s="17"/>
+      <c r="E6" s="10"/>
+      <c r="F6" s="9"/>
     </row>
     <row r="7" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A7" s="17">
+      <c r="A7" s="9">
         <v>4</v>
       </c>
-      <c r="B7" s="17" t="s">
+      <c r="B7" s="9" t="s">
         <v>131</v>
       </c>
-      <c r="C7" s="17" t="s">
+      <c r="C7" s="9" t="s">
         <v>132</v>
       </c>
       <c r="D7" t="s">
         <v>133</v>
       </c>
-      <c r="E7" s="18"/>
-      <c r="F7" s="17"/>
+      <c r="E7" s="10"/>
+      <c r="F7" s="9"/>
     </row>
     <row r="8" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A8" s="17">
+      <c r="A8" s="9">
         <v>5</v>
       </c>
-      <c r="B8" s="17" t="s">
+      <c r="B8" s="9" t="s">
         <v>134</v>
       </c>
-      <c r="C8" s="17" t="s">
+      <c r="C8" s="9" t="s">
         <v>135</v>
       </c>
       <c r="D8" t="s">
         <v>136</v>
       </c>
-      <c r="E8" s="18"/>
-      <c r="F8" s="17"/>
+      <c r="E8" s="10"/>
+      <c r="F8" s="9"/>
     </row>
     <row r="9" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A9" s="19"/>
-      <c r="B9" s="19"/>
-      <c r="C9" s="19"/>
-      <c r="D9" s="19"/>
-      <c r="E9" s="18"/>
-      <c r="F9" s="19"/>
-      <c r="G9" s="20"/>
-      <c r="H9" s="20"/>
+      <c r="A9" s="11"/>
+      <c r="B9" s="11"/>
+      <c r="C9" s="11"/>
+      <c r="D9" s="11"/>
+      <c r="E9" s="10"/>
+      <c r="F9" s="11"/>
+      <c r="G9" s="12"/>
+      <c r="H9" s="12"/>
     </row>
     <row r="10" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A10" s="19"/>
-      <c r="B10" s="19"/>
-      <c r="C10" s="19"/>
-      <c r="D10" s="19"/>
-      <c r="E10" s="18"/>
-      <c r="F10" s="19"/>
-      <c r="G10" s="20"/>
-      <c r="H10" s="20"/>
+      <c r="A10" s="11"/>
+      <c r="B10" s="11"/>
+      <c r="C10" s="11"/>
+      <c r="D10" s="11"/>
+      <c r="E10" s="10"/>
+      <c r="F10" s="11"/>
+      <c r="G10" s="12"/>
+      <c r="H10" s="12"/>
     </row>
   </sheetData>
   <mergeCells count="1">
